--- a/data/trans_orig/IP31KM13_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM13_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>109690</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>119351</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>68,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>110337</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>106381</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>112843</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>120592</t>
+          <t>114656</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87709</t>
+          <t>109250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132114</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>230929</t>
+          <t>224347</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193956</t>
+          <t>201513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242990</t>
+          <t>234038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13206</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38506</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7870</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49106</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>216552</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>208620</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>222627</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>175811</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>168000</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>179805</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>231981</t>
+          <t>169778</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223149</t>
+          <t>162604</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>237971</t>
+          <t>174444</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>407792</t>
+          <t>386329</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>396925</t>
+          <t>374909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>415924</t>
+          <t>394215</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14689</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8614</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22621</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10303</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18114</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>25842</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36709</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>139746</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>129229</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>148207</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>162634</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>151099</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>173637</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>80,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>155693</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146482</t>
+          <t>122173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164626</t>
+          <t>137981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>318328</t>
+          <t>271312</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301513</t>
+          <t>258345</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>333255</t>
+          <t>282573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26776</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18315</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37293</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25615</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14612</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37150</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27396</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53011</t>
+          <t>50248</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69826</t>
+          <t>63215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>160023</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>153456</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>163362</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>154370</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>147416</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>158720</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>170927</t>
+          <t>153802</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165304</t>
+          <t>147116</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174693</t>
+          <t>157888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>325297</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>316797</t>
+          <t>304769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330704</t>
+          <t>319227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2803</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12709</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>10149</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5799</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17103</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>626011</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>595829</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>640733</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>603153</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>586492</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>613665</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569803</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638897</t>
+          <t>557527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>695737</t>
+          <t>579751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1282346</t>
+          <t>1195814</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1247065</t>
+          <t>1168873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1302456</t>
+          <t>1214604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60813</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>46091</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>90995</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49981</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39469</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>66642</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105836</t>
+          <t>60681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>115521</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95411</t>
+          <t>90427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150802</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
